--- a/docs/INTERFACE.xlsx
+++ b/docs/INTERFACE.xlsx
@@ -1669,7 +1669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1698,7 +1698,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>(모든 엔드포인트 공통)  ·  -  ·  실패 응답의 본문 구조. 422 만 error_code·message 를 주고 그 밖은 detail 하나다</t>
+          <t xml:space="preserve">모든 엔드포인트 공통. 도메인 검증 422는 error_code·message, 요청 스키마 검증 422는 detail 배열을 반환한다.</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" ht="62" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
@@ -1790,11 +1790,11 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>422 응답에만 있다. 실패 사유를 나타내는 고정 코드다</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
+          <t xml:space="preserve">도메인 검증 422에 있다. 실패 사유를 나타내는 고정 코드다. UNSAFE_PARTITION_PREDICATE는 필수 WHERE 조건이 아닌 분할 IN을 뜻한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="8" t="n">
         <v>2</v>
       </c>
@@ -1835,11 +1835,11 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>422 응답에만 있다. 무엇을 고쳐야 하는지 설명한다</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+          <t xml:space="preserve">도메인 검증 422에 있다. 무엇을 고쳐야 하는지 설명한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t xml:space="preserve">string 또는 array</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t xml:space="preserve">1~N (배열일 때)</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>400·404·409·429·502 응답의 사람이 읽을 설명이다</t>
+          <t xml:space="preserve">400·404·409·429·502에서는 설명 문자열이다. 요청 스키마 검증 422에서는 loc·msg·type을 가진 객체 배열이며 input·ctx가 추가될 수 있다.</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart ns1:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>

--- a/docs/INTERFACE.xlsx
+++ b/docs/INTERFACE.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공통 오류 응답" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF-C-001 이관 작업 생성" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF-C-002 작업 진행률 조회" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF-C-003 작업 상세 조회" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF-C-004 작업 결과 조회" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF-C-005 작업 취소" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF-C-006 실패 파티션 재실행" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF-C-007 템플릿 쿼리 실행" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF-C-008 템플릿 목록 조회" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="개요" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="공통 오류 응답" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="IF-C-001 이관 작업 생성" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IF-C-002 작업 진행률 조회" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="IF-C-003 작업 상세 조회" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="IF-C-004 작업 결과 조회" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="IF-C-005 작업 취소" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="IF-C-006 실패 파티션 재실행" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="IF-C-007 템플릿 쿼리 실행" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="IF-C-008 템플릿 목록 조회" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="IF-C-009 템플릿 쿼리 건수 조회" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -696,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1069,6 +1070,40 @@
       </c>
       <c r="H13" s="4" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>IF-C-009</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>템플릿 쿼리 건수 조회</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>POST /query-count</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>동기</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1668,8 +1703,729 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="78" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>IF-C-009 — 템플릿 쿼리 건수 조회</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>POST /query-count  ·  동기  ·  서버 템플릿을 값으로 채워 만든 SELECT 의 결과 건수만 세어 돌려준다</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>필드명(한글)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>필드명(영문)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>부모필드명</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>데이터 타입</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>길이</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>반복 건수</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>입출력 구분</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>템플릿 식별자</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>template_id</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>가변</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>건수를 셀 템플릿 이름</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>파라미터 목록</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>0~N</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>[선택] 템플릿에 넣을 값들</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>파라미터 이름</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>가변</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>템플릿이 요구하는 이름</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>파라미터 값</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>가변</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>넣을 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>연산자 방향</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>sign</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>[선택] + 또는 -. 값의 부호가 아니라 SQL 연산자의 방향이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>데이터소스</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>datasource</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>가변</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>[선택] 어디에 물어볼지. impala·trino·greenplum·history</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>SQL 방언</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>sql_dialect</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>가변</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>[선택] 만들어진 SELECT 를 검사할 문법</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>템플릿 식별자</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>template_id</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>가변</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>실행한 템플릿 이름</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>데이터소스</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>datasource</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>가변</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>실제로 물어본 곳</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>템플릿 SQL</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>sql</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>가변</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>템플릿에서 만들어진 SELECT 전문. 감싸기 전의 원문이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>건수 SQL</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>count_sql</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>가변</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>실제로 실행한 건수 쿼리 전문</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>결과 건수</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>row_count</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>0 이상</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>SELECT 가 돌려줄 행의 총 건수</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>소요 시간</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>elapsed_ms</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>[선택] 건수 쿼리에 걸린 시간(밀리초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>실행 executor 주소</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>executed_by</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>가변</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>[선택] 대신 실행한 executor. coordinator 가 직접 했으면 비어 있다</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1698,7 +2454,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">모든 엔드포인트 공통. 도메인 검증 422는 error_code·message, 요청 스키마 검증 422는 detail 배열을 반환한다.</t>
+          <t>모든 엔드포인트 공통. 도메인 검증 422는 error_code·message, 요청 스키마 검증 422는 detail 배열을 반환한다.</t>
         </is>
       </c>
     </row>
@@ -1790,7 +2546,7 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">도메인 검증 422에 있다. 실패 사유를 나타내는 고정 코드다. UNSAFE_PARTITION_PREDICATE는 필수 WHERE 조건이 아닌 분할 IN을 뜻한다.</t>
+          <t>도메인 검증 422에 있다. 실패 사유를 나타내는 고정 코드다. UNSAFE_PARTITION_PREDICATE는 필수 WHERE 조건이 아닌 분할 IN을 뜻한다.</t>
         </is>
       </c>
     </row>
@@ -1835,7 +2591,7 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">도메인 검증 422에 있다. 무엇을 고쳐야 하는지 설명한다.</t>
+          <t>도메인 검증 422에 있다. 무엇을 고쳐야 하는지 설명한다.</t>
         </is>
       </c>
     </row>
@@ -1860,7 +2616,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">string 또는 array</t>
+          <t>string 또는 array</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1870,7 +2626,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1~N (배열일 때)</t>
+          <t>1~N (배열일 때)</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -1880,7 +2636,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">400·404·409·429·502에서는 설명 문자열이다. 요청 스키마 검증 422에서는 loc·msg·type을 가진 객체 배열이며 input·ctx가 추가될 수 있다.</t>
+          <t>400·404·409·429·502에서는 설명 문자열이다. 요청 스키마 검증 422에서는 loc·msg·type을 가진 객체 배열이며 input·ctx가 추가될 수 있다.</t>
         </is>
       </c>
     </row>
@@ -1892,7 +2648,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <tableParts count="1">
-    <tablePart ns1:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>

--- a/docs/INTERFACE.xlsx
+++ b/docs/INTERFACE.xlsx
@@ -2458,6 +2458,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2636,7 +2637,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>400·404·409·429·502에서는 설명 문자열이다. 요청 스키마 검증 422에서는 loc·msg·type을 가진 객체 배열이며 input·ctx가 추가될 수 있다.</t>
+          <t>400·404·409·429·502·503에서는 설명 문자열이다. 요청 스키마 검증 422에서는 loc·msg·type을 가진 객체 배열이며 input·ctx가 추가될 수 있다.</t>
         </is>
       </c>
     </row>
